--- a/Baseline/Purview/CATech_DLP_Label_Protection_Pack.xlsx
+++ b/Baseline/Purview/CATech_DLP_Label_Protection_Pack.xlsx
@@ -1,25 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jon/Desktop/LearnGraphAPI/Baseline/Purview/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D199248-2FD0-EE47-8EA7-401CFBC154C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="How To Use" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Build Matrix" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Naming Convention" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Licensing Gate" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Rollout Stages" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Verification Notes" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="How To Use" sheetId="1" r:id="rId1"/>
+    <sheet name="Build Matrix" sheetId="2" r:id="rId2"/>
+    <sheet name="Naming Convention" sheetId="3" r:id="rId3"/>
+    <sheet name="Licensing Gate" sheetId="4" r:id="rId4"/>
+    <sheet name="Rollout Stages" sheetId="5" r:id="rId5"/>
+    <sheet name="Verification Notes" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Build Matrix'!$A$2:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Build Matrix'!$A$2:$N$23</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -30,816 +46,812 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="267">
   <si>
-    <t xml:space="preserve">CATech DLP &amp; Sensitivity Label Protection Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trimmed build workbook — scoped to Confidential/Restricted labels, Financial, Medical, and CUI (custom), compiled from advisory conversation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use the Build Matrix tab as the source of truth for policy creation. Every row is one deployable policy: business outcome, detection method, rule structure, license gate, CATech-format policy name, and rollout path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naming convention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - [Workload] - [Pack/Scope] - [Action]. See the Naming Convention tab for full token reference and worked examples.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two policy layers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENERAL (label-based): Confidential/Restricted policies apply the same way regardless of why content is sensitive — driven by sensitivity label, not content pattern. VERTICAL (content-based): Financial, Medical, and CUI are driven by Sensitive Information Types (SITs) — triggers whether or not the item is labeled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every policy uses the standard two-rule structure: Low confidence / min instance count 1 / Any (discovery, tune from SIM volume) and High confidence / min instance count 10 / Any (enforcement anchor).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM is not skippable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Test with notifications' is a setting WITHIN simulation mode (policy tips on/off), not a separate mode — same policy object, same SIM action token. Run silent SIM first for a clean baseline, then flip on notifications, before promoting to WARN/BLOCK. See Rollout Stages tab for the compressed 1-week sequence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licensing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See the Licensing Gate tab — verified against the official Microsoft Purview service description as of the date on that tab. Two corrections vs. the original CloudCapsule/Tminus365 workbook are flagged in red — read the Verification Notes tab before using this with a client.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUI / Highly Regulated caveat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No built-in Microsoft SIT exists for CUI. The CUI policies here use a CUSTOM sensitive information type built from CUI markings. This is best-effort detection hygiene on a commercial tenant — it is NOT DFARS/NIST 800-171 compliance. That requires the underlying cloud environment to be FedRAMP Moderate-authorized (Office 365 GCC High), not a DLP policy. Do not represent this pack as DFARS-compliant to a client still on commercial M365.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 policies total — 12 general (label-based, all workloads), 1 anti-exfiltration (auto-forward), 6 vertical (Financial + Medical), 2 CUI custom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary (auto-counted from Build Matrix)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Premium-achievable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires E5 / Purview add-on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General (label-based) policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical (content-based) policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build Matrix — one deployable policy per row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pack/Scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detection Method</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule 1 (discovery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule 2 (high severity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">License</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy Name (CATech convention)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollout Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block Confidential-labeled content from being sent to external recipients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low confidence, min instance count 1, to Any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High confidence, min instance count 10, to Any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block external send; internal sharing unaffected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Confidential-ExternalBlock-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM &gt; tune &gt; BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label-as-DLP-condition confirmed core BP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/dlp-sensitivity-label-as-condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block Confidential-labeled files from being shared externally from SharePoint/OneDrive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block external sharing/access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - Confidential-ExternalBlock-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covers Teams file attachments automatically (auto-uploaded to SPO/OneDrive) — no separate Teams file policy needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restricted-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alert on any external send of Restricted-labeled content, regardless of sender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Restricted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block external send + alert security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Restricted-ExternalAlert-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Access control lives in the LABEL (published to restricted group only, encryption permissions set there). This DLP policy is the second layer / audit trail, not the primary control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alert on external sharing of Restricted-labeled files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block external sharing/access + alert security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - Restricted-ExternalAlert-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same label-first logic as EXO Restricted policy above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block Confidential content typed/pasted directly into Teams chat or channel messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block matching messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - TEAMS - Confidential-ExternalBlock-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM &gt; pilot &gt; BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only build for E5-tier clients. Not needed on BP — file-sharing exposure already caught by SPO/OneDrive policies above; this only adds message-body inspection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/office365/servicedescriptions/microsoft-365-service-descriptions/microsoft-365-tenantlevel-services-licensing-guidance/microsoft-purview-service-description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block/alert Restricted content typed/pasted directly into Teams messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block matching messages + alert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - TEAMS - Restricted-ExternalAlert-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same E5-only scoping as Confidential Teams policy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPILOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block Confidential content from being typed/pasted into Copilot Chat prompts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Confidential (prompt safeguarding)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block sensitive prompt submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - COPILOT - Confidential-PromptBlock-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM &gt; policy tip &gt; BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prompt-safeguarding DLP is available to ANY Copilot-licensed user on ANY M365 tier — confirmed via official service description. Requires Copilot license, not E5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/dlp-microsoft365-copilot-location-learn-about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block Restricted content from being typed/pasted into Copilot Chat prompts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Restricted (prompt safeguarding)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - COPILOT - Restricted-PromptBlock-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same prompt-level control as Confidential — BP-achievable with Copilot license.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude Confidential-labeled files from Copilot grounding (Copilot cannot read them as context)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude labeled content from grounding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - COPILOT - Confidential-GroundingExclude-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Different control from prompt-block above — this stops Copilot reading the file at all. E5/Purview add-on required, confirmed via service description.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude Restricted-labeled files from Copilot grounding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - COPILOT - Restricted-GroundingExclude-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same E5 gate as Confidential grounding-exclude.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDP-AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block pasting/uploading Confidential content into consumer AI apps (ChatGPT, Gemini, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Confidential (browser/endpoint)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block paste/upload to unapproved AI destinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EDP-AI - Confidential-BlockUpload-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audit &gt; WARN &gt; BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires Endpoint DLP (E5-tier) + devices onboarded to Purview/Defender. No BP-tier equivalent exists — genuine coverage gap to disclose on BP-only clients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/endpoint-dlp-create-policy-unauthorized-cloud-apps-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block pasting/uploading Restricted content into consumer AI apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content contains sensitivity label: Restricted (browser/endpoint)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EDP-AI - Restricted-BlockUpload-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same E5 + onboarding requirement as Confidential endpoint policy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-Exfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoForward-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop sensitive mail from being silently auto-forwarded outside the org (e.g. inbox rule to a personal address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Message type matches: Auto-forward AND Content contains sensitive SITs (PII/Finance/Healthcare)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block auto-forward + alert security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - AntiExfil-AutoForward-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-forward is a native Exchange DLP condition, independent of label/SIT detection — combine with content condition so legitimate auto-forwarding isn't blocked outright.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/dlp-exchange-conditions-and-actions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop credit card numbers and bank details from being emailed externally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in SITs: Credit card number; U.S. bank account number; ABA routing; SWIFT; IBAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block external send; allow justified override</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Financial-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content-based — triggers regardless of label.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/dlp-policy-reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop financial files from being shared externally via SharePoint/OneDrive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - Financial-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pairs with EXO Financial policy above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial-Accounting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warn (not block) Accounting before financial data leaves by email — approved workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy tip / warn with justification; no hard block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Financial-Accounting - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM &gt; WARN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception companion to the EXO Financial block policy — scoped to Accounting group only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop patient records/health identifiers from being emailed externally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in SITs: ICD-9-CM; ICD-10-CM; DEA Number AND a supporting PII SIT (matches records, not reference material)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Medical-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AND condition with PII SIT avoids matching medical reference docs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stop patient records from being shared externally via SharePoint/OneDrive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built-in SITs: ICD-9-CM; ICD-10-CM; DEA Number AND supporting PII SIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - Medical-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pairs with EXO Medical policy above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical-ClinicalBilling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warn (not block) Clinical &amp; Billing staff before patient data leaves by email — approved workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Medical-ClinicalBilling - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exception companion to the EXO Medical block policy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUI-Custom-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detect and flag CUI-marked content being emailed externally (hygiene, not compliance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUSTOM SIT built from CUI markings (e.g. CUI//SP-PRVCY category banners) — no built-in Microsoft SIT exists for CUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - CUI-Custom-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ Best-effort detection on a COMMERCIAL tenant only. Does NOT satisfy DFARS/NIST 800-171 — that requires the environment itself be FedRAMP Moderate-authorized (GCC High). Do not represent as DFARS-compliant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/compliance/regulatory/offering-dfars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detect and flag CUI-marked files shared externally via SharePoint/OneDrive (hygiene, not compliance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUSTOM SIT built from CUI markings — no built-in Microsoft SIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - CUI-Custom-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ Same compliance caveat as EXO CUI policy — pair together, same caveat applies to both.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech DLP Naming Convention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format: CATech - [Workload] - [Pack/Scope] - [Action]     Example: CATech - EXO - Financial-AllUsers - SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workload tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exchange Online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SharePoint and OneDrive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teams chat, channels, messages, files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft 365 Copilot / Copilot Chat policy location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDP-USB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint: removable media and print</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDP-CLOUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint: 3rd-party / personal cloud storage uploads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint / browser: generative AI app paste and upload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pack / Scope tokens (combines protection pack + target population)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential-AllUsers / Restricted-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label-based general policies — tenant-wide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial-AllUsers / Financial-[Team]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical — financial data; [Team] = approved-workflow warn scope, e.g. Accounting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical-AllUsers / Medical-[Team]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical — PHI/health identifiers; [Team] = approved-workflow warn scope, e.g. ClinicalBilling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertical — CUI marking detection (custom SIT, hygiene only, see caveat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AntiExfil-AutoForward-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anti-exfiltration — auto-forward + sensitive content combo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Label]-GroundingExclude-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot-specific — excludes labeled content from grounding (E5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Label]-PromptBlock-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot-specific — blocks label from prompt text (BP-achievable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Label]-BlockUpload-AllUsers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint/browser-specific — blocks paste/upload to consumer AI (E5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Action tokens (current mode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation mode — every policy starts here. Covers BOTH silent-SIM and SIM-with-notifications; the notifications toggle is a policy setting, not a naming distinction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WARN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy tips / warning, with or without justification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enforced block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worked examples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance email policy for all users, currently in simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - Financial-AllUsers - BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same policy after promotion to enforcement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - SPO - Financial-Accounting - WARN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance sharing policy warning Accounting on external shares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocking Confidential content typed into Copilot prompts, in simulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint policy simulating blocks of Restricted content pasted into ChatGPT/Gemini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATech - EXO - AntiExfil-AutoForward-AllUsers - BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enforced block on sensitive mail being auto-forwarded externally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licensing Gate — verified against Microsoft Purview service description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: learn.microsoft.com/office365/servicedescriptions/.../microsoft-purview-service-description — fetched live during this build. Re-verify before a proposal; Microsoft licensing changes without notice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5 / Purview add-on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exchange/SPO/OneDrive DLP (SITs, custom SITs, label-as-condition)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core DLP — the backbone of every EXO/SPO policy in this workbook.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teams DLP (message body inspection)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed gated to E5-tier. BP clients: skip — SPO/OneDrive already covers Teams file shares.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint DLP (USB, print, cloud upload, AI app paste/upload)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires device onboarding to Purview/Defender in addition to the license.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot DLP — restrict Copilot from PROCESSING files/emails (grounding)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Different control from prompt-safeguarding below — don't conflate the two when quoting a client.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot DLP — safeguard PROMPTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes — all tiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Available to any Copilot-licensed user regardless of M365 tier. CORRECTED vs. original workbook, which listed the whole Copilot pack as E5-gated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual sensitivity labeling + basic encryption (Do Not Forward, Encrypt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BP includes AIP Plan 1 — this is the mechanism the Restricted label's access control relies on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic (client/service-side) labeling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed E5-tier only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default/auto-label a SharePoint document library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTED vs. original workbook, which listed this as 'Business Premium+'. Official table gates this to E5/Purview Suite/IPG specifically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic Message Encryption (OME)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine for manual Restricted-label encryption.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Message Encryption (auto-policy by SIT, custom templates, revoke access)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is the E5 gate if 'alert on external file access' needs to mean auto-revoke rather than DLP-alert.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication Compliance (inappropriate use / AI prompt-response review)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also requires a Copilot license for Copilot interaction analysis specifically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollout Stages — 1-week compressed sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compression of the workbook's standard Stage 0/1 (normally 1–4 weeks) — reasonable for a small, well-scoped outcome set like this one, not the full stack at once.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Happens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exit Criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day 1–3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM — silent (no policy tips)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same policy object, same SIM action token. Pure baseline: read match volume, no user impact at all. This is where you set the Low rule's min-instance-count from real data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match volume understood; Low rule count tentatively set.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day 4–7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIM — with notifications / policy tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle the 'Show policy tips within simulation mode' setting on the same policy (not a new policy, not a renamed one). Users see tips, can report false positives, but nothing is blocked yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top false positives addressed; approved-workflow exceptions (Accounting, ClinicalBilling, etc.) documented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day 8+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WARN (pilot) then BLOCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rename the ACTION token in place: SIM → WARN → BLOCK. If a pack is still noisy at day 7, extend that pack only — don't promote everything on a fixed calendar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overrides rare and reviewed; false-positive rate acceptable to the business owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification Notes — flagged for human review before client use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot DLP licensing (corrected)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original workbook listed the entire Copilot pack as 'E5 / Purview suite add-on + Copilot license.' Official service description splits this: prompt-safeguarding DLP works on ANY tier with a Copilot license; only grounding/file-processing restriction needs E5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://learn.microsoft.com/purview/dlp-microsoft365-copilot-location-learn-about ; https://learn.microsoft.com/office365/servicedescriptions/microsoft-365-service-descriptions/microsoft-365-tenantlevel-services-licensing-guidance/microsoft-purview-service-description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SharePoint default/auto-labeling (corrected)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original workbook listed default-labeling a SharePoint library as 'Business Premium+ (validate auto-labeling).' Official service description gates this specifically to E5/Purview Suite/Information Protection &amp; Governance — not achievable on BP even with add-ons short of E5-tier IPG.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity label as DLP EXCEPTION on Business Premium — unresolved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Microsoft Q&amp;A community thread (not authoritative) claims BP's DLP engine evaluates labels as a block CONDITION but ignores them as an EXCEPTION/override — i.e., a 'DLP-exempt' label wouldn't actually bypass a block on BP the way it does on E5. Found nothing in official docs confirming or denying this at the exception level specifically. Test in a BP lab tenant before building client policies that rely on label-based DLP exceptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">learn.microsoft.com/answers/a/12151329 (community, unverified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUI / DFARS compliance boundary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No built-in Microsoft SIT exists for CUI — the CUI pack here uses a custom SIT. More importantly: DFARS/NIST 800-171 compliance requires the cloud environment itself be FedRAMP Moderate-authorized (Office 365 GCC High). A DLP policy in a commercial tenant is detection hygiene only and does not satisfy the requirement for an actual DoD contractor client.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-forward as a DLP condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed native Exchange DLP condition ('Message type matches: Auto-forward'), independent of SIT/label detection — usable on Business Premium as part of core Exchange DLP.</t>
+    <t>CATech DLP &amp; Sensitivity Label Protection Pack</t>
+  </si>
+  <si>
+    <t>Trimmed build workbook — scoped to Confidential/Restricted labels, Financial, Medical, and CUI (custom), compiled from advisory conversation.</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Use the Build Matrix tab as the source of truth for policy creation. Every row is one deployable policy: business outcome, detection method, rule structure, license gate, CATech-format policy name, and rollout path.</t>
+  </si>
+  <si>
+    <t>Naming convention</t>
+  </si>
+  <si>
+    <t>CATech - [Workload] - [Pack/Scope] - [Action]. See the Naming Convention tab for full token reference and worked examples.</t>
+  </si>
+  <si>
+    <t>Two policy layers</t>
+  </si>
+  <si>
+    <t>GENERAL (label-based): Confidential/Restricted policies apply the same way regardless of why content is sensitive — driven by sensitivity label, not content pattern. VERTICAL (content-based): Financial, Medical, and CUI are driven by Sensitive Information Types (SITs) — triggers whether or not the item is labeled.</t>
+  </si>
+  <si>
+    <t>Rule structure</t>
+  </si>
+  <si>
+    <t>Every policy uses the standard two-rule structure: Low confidence / min instance count 1 / Any (discovery, tune from SIM volume) and High confidence / min instance count 10 / Any (enforcement anchor).</t>
+  </si>
+  <si>
+    <t>SIM is not skippable</t>
+  </si>
+  <si>
+    <t>'Test with notifications' is a setting WITHIN simulation mode (policy tips on/off), not a separate mode — same policy object, same SIM action token. Run silent SIM first for a clean baseline, then flip on notifications, before promoting to WARN/BLOCK. See Rollout Stages tab for the compressed 1-week sequence.</t>
+  </si>
+  <si>
+    <t>Licensing</t>
+  </si>
+  <si>
+    <t>See the Licensing Gate tab — verified against the official Microsoft Purview service description as of the date on that tab. Two corrections vs. the original CloudCapsule/Tminus365 workbook are flagged in red — read the Verification Notes tab before using this with a client.</t>
+  </si>
+  <si>
+    <t>CUI / Highly Regulated caveat</t>
+  </si>
+  <si>
+    <t>No built-in Microsoft SIT exists for CUI. The CUI policies here use a CUSTOM sensitive information type built from CUI markings. This is best-effort detection hygiene on a commercial tenant — it is NOT DFARS/NIST 800-171 compliance. That requires the underlying cloud environment to be FedRAMP Moderate-authorized (Office 365 GCC High), not a DLP policy. Do not represent this pack as DFARS-compliant to a client still on commercial M365.</t>
+  </si>
+  <si>
+    <t>Policy count</t>
+  </si>
+  <si>
+    <t>21 policies total — 12 general (label-based, all workloads), 1 anti-exfiltration (auto-forward), 6 vertical (Financial + Medical), 2 CUI custom.</t>
+  </si>
+  <si>
+    <t>Summary (auto-counted from Build Matrix)</t>
+  </si>
+  <si>
+    <t>Total policies</t>
+  </si>
+  <si>
+    <t>Business Premium-achievable</t>
+  </si>
+  <si>
+    <t>Requires E5 / Purview add-on</t>
+  </si>
+  <si>
+    <t>General (label-based) policies</t>
+  </si>
+  <si>
+    <t>Vertical (content-based) policies</t>
+  </si>
+  <si>
+    <t>Build Matrix — one deployable policy per row</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Workload</t>
+  </si>
+  <si>
+    <t>Pack/Scope</t>
+  </si>
+  <si>
+    <t>Business Outcome</t>
+  </si>
+  <si>
+    <t>Detection Method</t>
+  </si>
+  <si>
+    <t>Rule 1 (discovery)</t>
+  </si>
+  <si>
+    <t>Rule 2 (high severity)</t>
+  </si>
+  <si>
+    <t>Target Action</t>
+  </si>
+  <si>
+    <t>License</t>
+  </si>
+  <si>
+    <t>Policy Name (CATech convention)</t>
+  </si>
+  <si>
+    <t>Rollout Path</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Microsoft Reference</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>Confidential-AllUsers</t>
+  </si>
+  <si>
+    <t>Block Confidential-labeled content from being sent to external recipients</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Confidential</t>
+  </si>
+  <si>
+    <t>Low confidence, min instance count 1, to Any</t>
+  </si>
+  <si>
+    <t>High confidence, min instance count 10, to Any</t>
+  </si>
+  <si>
+    <t>Block external send; internal sharing unaffected</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Confidential-ExternalBlock-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>SIM &gt; tune &gt; BLOCK</t>
+  </si>
+  <si>
+    <t>Label-as-DLP-condition confirmed core BP.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/dlp-sensitivity-label-as-condition</t>
+  </si>
+  <si>
+    <t>SPO</t>
+  </si>
+  <si>
+    <t>Block Confidential-labeled files from being shared externally from SharePoint/OneDrive</t>
+  </si>
+  <si>
+    <t>Block external sharing/access</t>
+  </si>
+  <si>
+    <t>CATech - SPO - Confidential-ExternalBlock-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Covers Teams file attachments automatically (auto-uploaded to SPO/OneDrive) — no separate Teams file policy needed.</t>
+  </si>
+  <si>
+    <t>Restricted-AllUsers</t>
+  </si>
+  <si>
+    <t>Alert on any external send of Restricted-labeled content, regardless of sender</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Restricted</t>
+  </si>
+  <si>
+    <t>Block external send + alert security</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Restricted-ExternalAlert-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Access control lives in the LABEL (published to restricted group only, encryption permissions set there). This DLP policy is the second layer / audit trail, not the primary control.</t>
+  </si>
+  <si>
+    <t>Alert on external sharing of Restricted-labeled files</t>
+  </si>
+  <si>
+    <t>Block external sharing/access + alert security</t>
+  </si>
+  <si>
+    <t>CATech - SPO - Restricted-ExternalAlert-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Same label-first logic as EXO Restricted policy above.</t>
+  </si>
+  <si>
+    <t>TEAMS</t>
+  </si>
+  <si>
+    <t>Block Confidential content typed/pasted directly into Teams chat or channel messages</t>
+  </si>
+  <si>
+    <t>Block matching messages</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>CATech - TEAMS - Confidential-ExternalBlock-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>SIM &gt; pilot &gt; BLOCK</t>
+  </si>
+  <si>
+    <t>Only build for E5-tier clients. Not needed on BP — file-sharing exposure already caught by SPO/OneDrive policies above; this only adds message-body inspection.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/office365/servicedescriptions/microsoft-365-service-descriptions/microsoft-365-tenantlevel-services-licensing-guidance/microsoft-purview-service-description</t>
+  </si>
+  <si>
+    <t>Block/alert Restricted content typed/pasted directly into Teams messages</t>
+  </si>
+  <si>
+    <t>Block matching messages + alert</t>
+  </si>
+  <si>
+    <t>CATech - TEAMS - Restricted-ExternalAlert-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Same E5-only scoping as Confidential Teams policy.</t>
+  </si>
+  <si>
+    <t>COPILOT</t>
+  </si>
+  <si>
+    <t>Block Confidential content from being typed/pasted into Copilot Chat prompts</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Confidential (prompt safeguarding)</t>
+  </si>
+  <si>
+    <t>Block sensitive prompt submission</t>
+  </si>
+  <si>
+    <t>CATech - COPILOT - Confidential-PromptBlock-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>SIM &gt; policy tip &gt; BLOCK</t>
+  </si>
+  <si>
+    <t>Prompt-safeguarding DLP is available to ANY Copilot-licensed user on ANY M365 tier — confirmed via official service description. Requires Copilot license, not E5.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/dlp-microsoft365-copilot-location-learn-about</t>
+  </si>
+  <si>
+    <t>Block Restricted content from being typed/pasted into Copilot Chat prompts</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Restricted (prompt safeguarding)</t>
+  </si>
+  <si>
+    <t>CATech - COPILOT - Restricted-PromptBlock-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Same prompt-level control as Confidential — BP-achievable with Copilot license.</t>
+  </si>
+  <si>
+    <t>Exclude Confidential-labeled files from Copilot grounding (Copilot cannot read them as context)</t>
+  </si>
+  <si>
+    <t>Exclude labeled content from grounding</t>
+  </si>
+  <si>
+    <t>CATech - COPILOT - Confidential-GroundingExclude-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Different control from prompt-block above — this stops Copilot reading the file at all. E5/Purview add-on required, confirmed via service description.</t>
+  </si>
+  <si>
+    <t>Exclude Restricted-labeled files from Copilot grounding</t>
+  </si>
+  <si>
+    <t>CATech - COPILOT - Restricted-GroundingExclude-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Same E5 gate as Confidential grounding-exclude.</t>
+  </si>
+  <si>
+    <t>EDP-AI</t>
+  </si>
+  <si>
+    <t>Block pasting/uploading Confidential content into consumer AI apps (ChatGPT, Gemini, etc.)</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Confidential (browser/endpoint)</t>
+  </si>
+  <si>
+    <t>Block paste/upload to unapproved AI destinations</t>
+  </si>
+  <si>
+    <t>CATech - EDP-AI - Confidential-BlockUpload-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Audit &gt; WARN &gt; BLOCK</t>
+  </si>
+  <si>
+    <t>Requires Endpoint DLP (E5-tier) + devices onboarded to Purview/Defender. No BP-tier equivalent exists — genuine coverage gap to disclose on BP-only clients.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/endpoint-dlp-create-policy-unauthorized-cloud-apps-services</t>
+  </si>
+  <si>
+    <t>Block pasting/uploading Restricted content into consumer AI apps</t>
+  </si>
+  <si>
+    <t>Content contains sensitivity label: Restricted (browser/endpoint)</t>
+  </si>
+  <si>
+    <t>CATech - EDP-AI - Restricted-BlockUpload-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Same E5 + onboarding requirement as Confidential endpoint policy.</t>
+  </si>
+  <si>
+    <t>Anti-Exfil</t>
+  </si>
+  <si>
+    <t>AutoForward-AllUsers</t>
+  </si>
+  <si>
+    <t>Stop sensitive mail from being silently auto-forwarded outside the org (e.g. inbox rule to a personal address)</t>
+  </si>
+  <si>
+    <t>Message type matches: Auto-forward AND Content contains sensitive SITs (PII/Finance/Healthcare)</t>
+  </si>
+  <si>
+    <t>Block auto-forward + alert security</t>
+  </si>
+  <si>
+    <t>CATech - EXO - AntiExfil-AutoForward-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Auto-forward is a native Exchange DLP condition, independent of label/SIT detection — combine with content condition so legitimate auto-forwarding isn't blocked outright.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/dlp-exchange-conditions-and-actions</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t>Financial-AllUsers</t>
+  </si>
+  <si>
+    <t>Stop credit card numbers and bank details from being emailed externally</t>
+  </si>
+  <si>
+    <t>Built-in SITs: Credit card number; U.S. bank account number; ABA routing; SWIFT; IBAN</t>
+  </si>
+  <si>
+    <t>Block external send; allow justified override</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Financial-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Content-based — triggers regardless of label.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/dlp-policy-reference</t>
+  </si>
+  <si>
+    <t>Stop financial files from being shared externally via SharePoint/OneDrive</t>
+  </si>
+  <si>
+    <t>CATech - SPO - Financial-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Pairs with EXO Financial policy above.</t>
+  </si>
+  <si>
+    <t>Financial-Accounting</t>
+  </si>
+  <si>
+    <t>Warn (not block) Accounting before financial data leaves by email — approved workflow</t>
+  </si>
+  <si>
+    <t>Policy tip / warn with justification; no hard block</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Financial-Accounting - SIM</t>
+  </si>
+  <si>
+    <t>SIM &gt; WARN</t>
+  </si>
+  <si>
+    <t>Exception companion to the EXO Financial block policy — scoped to Accounting group only.</t>
+  </si>
+  <si>
+    <t>Medical-AllUsers</t>
+  </si>
+  <si>
+    <t>Stop patient records/health identifiers from being emailed externally</t>
+  </si>
+  <si>
+    <t>Built-in SITs: ICD-9-CM; ICD-10-CM; DEA Number AND a supporting PII SIT (matches records, not reference material)</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Medical-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>AND condition with PII SIT avoids matching medical reference docs.</t>
+  </si>
+  <si>
+    <t>Stop patient records from being shared externally via SharePoint/OneDrive</t>
+  </si>
+  <si>
+    <t>Built-in SITs: ICD-9-CM; ICD-10-CM; DEA Number AND supporting PII SIT</t>
+  </si>
+  <si>
+    <t>CATech - SPO - Medical-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Pairs with EXO Medical policy above.</t>
+  </si>
+  <si>
+    <t>Medical-ClinicalBilling</t>
+  </si>
+  <si>
+    <t>Warn (not block) Clinical &amp; Billing staff before patient data leaves by email — approved workflow</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Medical-ClinicalBilling - SIM</t>
+  </si>
+  <si>
+    <t>Exception companion to the EXO Medical block policy.</t>
+  </si>
+  <si>
+    <t>CUI-Custom-AllUsers</t>
+  </si>
+  <si>
+    <t>Detect and flag CUI-marked content being emailed externally (hygiene, not compliance)</t>
+  </si>
+  <si>
+    <t>CUSTOM SIT built from CUI markings (e.g. CUI//SP-PRVCY category banners) — no built-in Microsoft SIT exists for CUI</t>
+  </si>
+  <si>
+    <t>CATech - EXO - CUI-Custom-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>⚠ Best-effort detection on a COMMERCIAL tenant only. Does NOT satisfy DFARS/NIST 800-171 — that requires the environment itself be FedRAMP Moderate-authorized (GCC High). Do not represent as DFARS-compliant.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/compliance/regulatory/offering-dfars</t>
+  </si>
+  <si>
+    <t>Detect and flag CUI-marked files shared externally via SharePoint/OneDrive (hygiene, not compliance)</t>
+  </si>
+  <si>
+    <t>CUSTOM SIT built from CUI markings — no built-in Microsoft SIT</t>
+  </si>
+  <si>
+    <t>CATech - SPO - CUI-Custom-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>⚠ Same compliance caveat as EXO CUI policy — pair together, same caveat applies to both.</t>
+  </si>
+  <si>
+    <t>CATech DLP Naming Convention</t>
+  </si>
+  <si>
+    <t>Format: CATech - [Workload] - [Pack/Scope] - [Action]     Example: CATech - EXO - Financial-AllUsers - SIM</t>
+  </si>
+  <si>
+    <t>Workload tokens</t>
+  </si>
+  <si>
+    <t>Exchange Online</t>
+  </si>
+  <si>
+    <t>SharePoint and OneDrive</t>
+  </si>
+  <si>
+    <t>Teams chat, channels, messages, files</t>
+  </si>
+  <si>
+    <t>Microsoft 365 Copilot / Copilot Chat policy location</t>
+  </si>
+  <si>
+    <t>EDP-USB</t>
+  </si>
+  <si>
+    <t>Endpoint: removable media and print</t>
+  </si>
+  <si>
+    <t>EDP-CLOUD</t>
+  </si>
+  <si>
+    <t>Endpoint: 3rd-party / personal cloud storage uploads</t>
+  </si>
+  <si>
+    <t>Endpoint / browser: generative AI app paste and upload</t>
+  </si>
+  <si>
+    <t>Pack / Scope tokens (combines protection pack + target population)</t>
+  </si>
+  <si>
+    <t>Confidential-AllUsers / Restricted-AllUsers</t>
+  </si>
+  <si>
+    <t>Label-based general policies — tenant-wide</t>
+  </si>
+  <si>
+    <t>Financial-AllUsers / Financial-[Team]</t>
+  </si>
+  <si>
+    <t>Vertical — financial data; [Team] = approved-workflow warn scope, e.g. Accounting</t>
+  </si>
+  <si>
+    <t>Medical-AllUsers / Medical-[Team]</t>
+  </si>
+  <si>
+    <t>Vertical — PHI/health identifiers; [Team] = approved-workflow warn scope, e.g. ClinicalBilling</t>
+  </si>
+  <si>
+    <t>Vertical — CUI marking detection (custom SIT, hygiene only, see caveat)</t>
+  </si>
+  <si>
+    <t>AntiExfil-AutoForward-AllUsers</t>
+  </si>
+  <si>
+    <t>Anti-exfiltration — auto-forward + sensitive content combo</t>
+  </si>
+  <si>
+    <t>[Label]-GroundingExclude-AllUsers</t>
+  </si>
+  <si>
+    <t>Copilot-specific — excludes labeled content from grounding (E5)</t>
+  </si>
+  <si>
+    <t>[Label]-PromptBlock-AllUsers</t>
+  </si>
+  <si>
+    <t>Copilot-specific — blocks label from prompt text (BP-achievable)</t>
+  </si>
+  <si>
+    <t>[Label]-BlockUpload-AllUsers</t>
+  </si>
+  <si>
+    <t>Endpoint/browser-specific — blocks paste/upload to consumer AI (E5)</t>
+  </si>
+  <si>
+    <t>Action tokens (current mode)</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Simulation mode — every policy starts here. Covers BOTH silent-SIM and SIM-with-notifications; the notifications toggle is a policy setting, not a naming distinction.</t>
+  </si>
+  <si>
+    <t>WARN</t>
+  </si>
+  <si>
+    <t>Policy tips / warning, with or without justification</t>
+  </si>
+  <si>
+    <t>BLOCK</t>
+  </si>
+  <si>
+    <t>Enforced block</t>
+  </si>
+  <si>
+    <t>Worked examples</t>
+  </si>
+  <si>
+    <t>Finance email policy for all users, currently in simulation</t>
+  </si>
+  <si>
+    <t>CATech - EXO - Financial-AllUsers - BLOCK</t>
+  </si>
+  <si>
+    <t>Same policy after promotion to enforcement</t>
+  </si>
+  <si>
+    <t>CATech - SPO - Financial-Accounting - WARN</t>
+  </si>
+  <si>
+    <t>Finance sharing policy warning Accounting on external shares</t>
+  </si>
+  <si>
+    <t>Blocking Confidential content typed into Copilot prompts, in simulation</t>
+  </si>
+  <si>
+    <t>Endpoint policy simulating blocks of Restricted content pasted into ChatGPT/Gemini</t>
+  </si>
+  <si>
+    <t>CATech - EXO - AntiExfil-AutoForward-AllUsers - BLOCK</t>
+  </si>
+  <si>
+    <t>Enforced block on sensitive mail being auto-forwarded externally</t>
+  </si>
+  <si>
+    <t>Licensing Gate — verified against Microsoft Purview service description</t>
+  </si>
+  <si>
+    <t>Source: learn.microsoft.com/office365/servicedescriptions/.../microsoft-purview-service-description — fetched live during this build. Re-verify before a proposal; Microsoft licensing changes without notice.</t>
+  </si>
+  <si>
+    <t>Capability</t>
+  </si>
+  <si>
+    <t>Business Premium</t>
+  </si>
+  <si>
+    <t>E5 / Purview add-on</t>
+  </si>
+  <si>
+    <t>Exchange/SPO/OneDrive DLP (SITs, custom SITs, label-as-condition)</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Core DLP — the backbone of every EXO/SPO policy in this workbook.</t>
+  </si>
+  <si>
+    <t>Teams DLP (message body inspection)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Confirmed gated to E5-tier. BP clients: skip — SPO/OneDrive already covers Teams file shares.</t>
+  </si>
+  <si>
+    <t>Endpoint DLP (USB, print, cloud upload, AI app paste/upload)</t>
+  </si>
+  <si>
+    <t>Requires device onboarding to Purview/Defender in addition to the license.</t>
+  </si>
+  <si>
+    <t>Copilot DLP — restrict Copilot from PROCESSING files/emails (grounding)</t>
+  </si>
+  <si>
+    <t>Different control from prompt-safeguarding below — don't conflate the two when quoting a client.</t>
+  </si>
+  <si>
+    <t>Copilot DLP — safeguard PROMPTS</t>
+  </si>
+  <si>
+    <t>Yes — all tiers</t>
+  </si>
+  <si>
+    <t>Available to any Copilot-licensed user regardless of M365 tier. CORRECTED vs. original workbook, which listed the whole Copilot pack as E5-gated.</t>
+  </si>
+  <si>
+    <t>Manual sensitivity labeling + basic encryption (Do Not Forward, Encrypt)</t>
+  </si>
+  <si>
+    <t>BP includes AIP Plan 1 — this is the mechanism the Restricted label's access control relies on.</t>
+  </si>
+  <si>
+    <t>Automatic (client/service-side) labeling</t>
+  </si>
+  <si>
+    <t>Confirmed E5-tier only.</t>
+  </si>
+  <si>
+    <t>Default/auto-label a SharePoint document library</t>
+  </si>
+  <si>
+    <t>CORRECTED vs. original workbook, which listed this as 'Business Premium+'. Official table gates this to E5/Purview Suite/IPG specifically.</t>
+  </si>
+  <si>
+    <t>Basic Message Encryption (OME)</t>
+  </si>
+  <si>
+    <t>Fine for manual Restricted-label encryption.</t>
+  </si>
+  <si>
+    <t>Advanced Message Encryption (auto-policy by SIT, custom templates, revoke access)</t>
+  </si>
+  <si>
+    <t>This is the E5 gate if 'alert on external file access' needs to mean auto-revoke rather than DLP-alert.</t>
+  </si>
+  <si>
+    <t>Communication Compliance (inappropriate use / AI prompt-response review)</t>
+  </si>
+  <si>
+    <t>Also requires a Copilot license for Copilot interaction analysis specifically.</t>
+  </si>
+  <si>
+    <t>Rollout Stages — 1-week compressed sequence</t>
+  </si>
+  <si>
+    <t>Compression of the workbook's standard Stage 0/1 (normally 1–4 weeks) — reasonable for a small, well-scoped outcome set like this one, not the full stack at once.</t>
+  </si>
+  <si>
+    <t>Day(s)</t>
+  </si>
+  <si>
+    <t>Policy Mode</t>
+  </si>
+  <si>
+    <t>What Happens</t>
+  </si>
+  <si>
+    <t>Exit Criteria</t>
+  </si>
+  <si>
+    <t>SIM — silent (no policy tips)</t>
+  </si>
+  <si>
+    <t>Same policy object, same SIM action token. Pure baseline: read match volume, no user impact at all. This is where you set the Low rule's min-instance-count from real data.</t>
+  </si>
+  <si>
+    <t>Match volume understood; Low rule count tentatively set.</t>
+  </si>
+  <si>
+    <t>SIM — with notifications / policy tips</t>
+  </si>
+  <si>
+    <t>Toggle the 'Show policy tips within simulation mode' setting on the same policy (not a new policy, not a renamed one). Users see tips, can report false positives, but nothing is blocked yet.</t>
+  </si>
+  <si>
+    <t>Top false positives addressed; approved-workflow exceptions (Accounting, ClinicalBilling, etc.) documented.</t>
+  </si>
+  <si>
+    <t>WARN (pilot) then BLOCK</t>
+  </si>
+  <si>
+    <t>Rename the ACTION token in place: SIM → WARN → BLOCK. If a pack is still noisy at day 7, extend that pack only — don't promote everything on a fixed calendar.</t>
+  </si>
+  <si>
+    <t>Overrides rare and reviewed; false-positive rate acceptable to the business owner.</t>
+  </si>
+  <si>
+    <t>Verification Notes — flagged for human review before client use</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Copilot DLP licensing (corrected)</t>
+  </si>
+  <si>
+    <t>Original workbook listed the entire Copilot pack as 'E5 / Purview suite add-on + Copilot license.' Official service description splits this: prompt-safeguarding DLP works on ANY tier with a Copilot license; only grounding/file-processing restriction needs E5.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/purview/dlp-microsoft365-copilot-location-learn-about ; https://learn.microsoft.com/office365/servicedescriptions/microsoft-365-service-descriptions/microsoft-365-tenantlevel-services-licensing-guidance/microsoft-purview-service-description</t>
+  </si>
+  <si>
+    <t>SharePoint default/auto-labeling (corrected)</t>
+  </si>
+  <si>
+    <t>Original workbook listed default-labeling a SharePoint library as 'Business Premium+ (validate auto-labeling).' Official service description gates this specifically to E5/Purview Suite/Information Protection &amp; Governance — not achievable on BP even with add-ons short of E5-tier IPG.</t>
+  </si>
+  <si>
+    <t>Sensitivity label as DLP EXCEPTION on Business Premium — unresolved</t>
+  </si>
+  <si>
+    <t>A Microsoft Q&amp;A community thread (not authoritative) claims BP's DLP engine evaluates labels as a block CONDITION but ignores them as an EXCEPTION/override — i.e., a 'DLP-exempt' label wouldn't actually bypass a block on BP the way it does on E5. Found nothing in official docs confirming or denying this at the exception level specifically. Test in a BP lab tenant before building client policies that rely on label-based DLP exceptions.</t>
+  </si>
+  <si>
+    <t>learn.microsoft.com/answers/a/12151329 (community, unverified)</t>
+  </si>
+  <si>
+    <t>CUI / DFARS compliance boundary</t>
+  </si>
+  <si>
+    <t>No built-in Microsoft SIT exists for CUI — the CUI pack here uses a custom SIT. More importantly: DFARS/NIST 800-171 compliance requires the cloud environment itself be FedRAMP Moderate-authorized (Office 365 GCC High). A DLP policy in a commercial tenant is detection hygiene only and does not satisfy the requirement for an actual DoD contractor client.</t>
+  </si>
+  <si>
+    <t>Auto-forward as a DLP condition</t>
+  </si>
+  <si>
+    <t>Confirmed native Exchange DLP condition ('Message type matches: Auto-forward'), independent of SIT/label detection — usable on Business Premium as part of core Exchange DLP.</t>
+  </si>
+  <si>
+    <t>Day 1–7</t>
+  </si>
+  <si>
+    <t>Day 8-14</t>
+  </si>
+  <si>
+    <t>Day 14 - 31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,62 +862,46 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -941,14 +937,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -964,154 +960,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1170,51 +1065,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1222,12 +1129,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1256,7 +1163,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1277,7 +1184,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1328,7 +1235,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1346,149 +1253,148 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <f aca="false">COUNTA('Build Matrix'!A3:A100)</f>
+      <c r="B14" s="8">
+        <f>COUNTA('Build Matrix'!A3:A100)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="7" t="n">
-        <f aca="false">COUNTIF('Build Matrix'!J3:J100,"BP")</f>
+      <c r="B15" s="8">
+        <f>COUNTIF('Build Matrix'!J3:J100,"BP")</f>
         <v>15</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="7" t="n">
-        <f aca="false">COUNTIF('Build Matrix'!J3:J100,"E5")</f>
+      <c r="B16" s="8">
+        <f>COUNTIF('Build Matrix'!J3:J100,"E5")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="7" t="n">
-        <f aca="false">COUNTIF('Build Matrix'!B3:B100,"General")</f>
+      <c r="B17" s="8">
+        <f>COUNTIF('Build Matrix'!B3:B100,"General")</f>
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="7" t="n">
-        <f aca="false">COUNTIF('Build Matrix'!B3:B100,"Vertical")</f>
+      <c r="B18" s="8">
+        <f>COUNTIF('Build Matrix'!B3:B100,"Vertical")</f>
         <v>8</v>
       </c>
     </row>
@@ -1497,56 +1403,48 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="34"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1488,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
+    <row r="3" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1634,8 +1532,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+    <row r="4" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -1678,8 +1576,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -1722,8 +1620,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+    <row r="6" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
@@ -1766,8 +1664,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+    <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1810,8 +1708,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+    <row r="8" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1854,8 +1752,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+    <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -1898,8 +1796,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+    <row r="10" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
@@ -1942,8 +1840,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+    <row r="11" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1986,8 +1884,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+    <row r="12" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -2030,8 +1928,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+    <row r="13" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
         <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -2074,8 +1972,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="n">
+    <row r="14" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
         <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -2118,8 +2016,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
+    <row r="15" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
@@ -2162,8 +2060,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+    <row r="16" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
@@ -2206,8 +2104,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
+    <row r="17" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -2250,8 +2148,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
+    <row r="18" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
@@ -2294,8 +2192,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
+    <row r="19" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
@@ -2338,8 +2236,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
+    <row r="20" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -2382,8 +2280,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
+    <row r="21" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -2426,8 +2324,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="n">
+    <row r="22" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12">
         <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
@@ -2470,8 +2368,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="n">
+    <row r="23" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12">
         <v>21</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -2515,52 +2413,43 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N23"/>
+  <autoFilter ref="A2:N23" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>40</v>
       </c>
@@ -2568,7 +2457,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>52</v>
       </c>
@@ -2576,7 +2465,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>67</v>
       </c>
@@ -2584,7 +2473,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>79</v>
       </c>
@@ -2592,7 +2481,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>165</v>
       </c>
@@ -2600,7 +2489,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>167</v>
       </c>
@@ -2608,7 +2497,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>98</v>
       </c>
@@ -2616,13 +2505,13 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B13" s="8"/>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>171</v>
       </c>
@@ -2630,7 +2519,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>173</v>
       </c>
@@ -2638,7 +2527,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>175</v>
       </c>
@@ -2646,7 +2535,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>148</v>
       </c>
@@ -2654,7 +2543,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>178</v>
       </c>
@@ -2662,7 +2551,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>180</v>
       </c>
@@ -2670,7 +2559,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>182</v>
       </c>
@@ -2678,7 +2567,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>184</v>
       </c>
@@ -2686,13 +2575,13 @@
         <v>185</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>187</v>
       </c>
@@ -2700,7 +2589,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>189</v>
       </c>
@@ -2708,7 +2597,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>191</v>
       </c>
@@ -2716,13 +2605,13 @@
         <v>192</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>123</v>
       </c>
@@ -2730,7 +2619,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" ht="28" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>195</v>
       </c>
@@ -2738,7 +2627,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:2" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
         <v>197</v>
       </c>
@@ -2746,7 +2635,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:2" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
         <v>83</v>
       </c>
@@ -2754,7 +2643,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:2" ht="28" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
         <v>108</v>
       </c>
@@ -2762,7 +2651,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:2" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
         <v>201</v>
       </c>
@@ -2772,46 +2661,38 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>204</v>
       </c>
@@ -2819,7 +2700,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>205</v>
       </c>
@@ -2833,7 +2714,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>208</v>
       </c>
@@ -2847,7 +2728,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>211</v>
       </c>
@@ -2861,7 +2742,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>214</v>
       </c>
@@ -2875,7 +2756,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>216</v>
       </c>
@@ -2889,7 +2770,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>218</v>
       </c>
@@ -2903,7 +2784,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>221</v>
       </c>
@@ -2917,7 +2798,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>223</v>
       </c>
@@ -2931,7 +2812,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>225</v>
       </c>
@@ -2945,7 +2826,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>227</v>
       </c>
@@ -2959,7 +2840,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>229</v>
       </c>
@@ -2973,7 +2854,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>231</v>
       </c>
@@ -2992,39 +2873,31 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>234</v>
       </c>
@@ -3032,7 +2905,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>235</v>
       </c>
@@ -3046,46 +2919,46 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="C6" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="D6" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3093,97 +2966,89 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>259</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B7" s="12" t="s">
         <v>261</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>117</v>
@@ -3193,12 +3058,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0000-bc88714345d2}" enabled="1" method="Privileged" siteId="{86600c1e-803d-49b9-a963-036358886be9}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>